--- a/excel_files/15.7.1.2.xlsx
+++ b/excel_files/15.7.1.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71957D2F-789B-48FF-9ABD-B551C0432297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -135,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -158,11 +159,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -182,9 +189,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -222,9 +229,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -259,7 +266,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -294,7 +301,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -467,15 +474,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.42578125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -485,21 +492,19 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -514,8 +519,9 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
+      <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -558,8 +564,11 @@
       <c r="N4" s="5">
         <v>2023</v>
       </c>
+      <c r="O4" s="10">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
@@ -601,6 +610,9 @@
       </c>
       <c r="N5" s="7">
         <v>553</v>
+      </c>
+      <c r="O5" s="11">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
